--- a/etf_holdings/2026-09-02_00993A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-02_00993A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:21</t>
+          <t>2026-09-02 00:56:51</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:21</t>
+          <t>2026-09-02 00:56:51</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:21</t>
+          <t>2026-09-02 00:56:51</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:21</t>
+          <t>2026-09-02 00:56:51</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:21</t>
+          <t>2026-09-02 00:56:51</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:21</t>
+          <t>2026-09-02 00:56:51</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:21</t>
+          <t>2026-09-02 00:56:51</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:21</t>
+          <t>2026-09-02 00:56:51</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:21</t>
+          <t>2026-09-02 00:56:51</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:21</t>
+          <t>2026-09-02 00:56:51</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:21</t>
+          <t>2026-09-02 00:56:51</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:21</t>
+          <t>2026-09-02 00:56:51</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:21</t>
+          <t>2026-09-02 00:56:51</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:21</t>
+          <t>2026-09-02 00:56:51</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:21</t>
+          <t>2026-09-02 00:56:51</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:22</t>
+          <t>2026-09-02 00:56:52</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:22</t>
+          <t>2026-09-02 00:56:52</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:22</t>
+          <t>2026-09-02 00:56:52</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:22</t>
+          <t>2026-09-02 00:56:52</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:22</t>
+          <t>2026-09-02 00:56:52</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:22</t>
+          <t>2026-09-02 00:56:52</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:22</t>
+          <t>2026-09-02 00:56:52</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:22</t>
+          <t>2026-09-02 00:56:52</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:22</t>
+          <t>2026-09-02 00:56:52</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:22</t>
+          <t>2026-09-02 00:56:52</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:22</t>
+          <t>2026-09-02 00:56:52</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:22</t>
+          <t>2026-09-02 00:56:52</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:22</t>
+          <t>2026-09-02 00:56:52</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:22</t>
+          <t>2026-09-02 00:56:52</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:22</t>
+          <t>2026-09-02 00:56:52</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:24</t>
+          <t>2026-09-02 00:56:54</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:24</t>
+          <t>2026-09-02 00:56:54</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:24</t>
+          <t>2026-09-02 00:56:54</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:24</t>
+          <t>2026-09-02 00:56:54</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:24</t>
+          <t>2026-09-02 00:56:54</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:24</t>
+          <t>2026-09-02 00:56:54</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:24</t>
+          <t>2026-09-02 00:56:54</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:24</t>
+          <t>2026-09-02 00:56:54</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:24</t>
+          <t>2026-09-02 00:56:54</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:24</t>
+          <t>2026-09-02 00:56:54</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:24</t>
+          <t>2026-09-02 00:56:54</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:24</t>
+          <t>2026-09-02 00:56:54</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:24</t>
+          <t>2026-09-02 00:56:54</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:24</t>
+          <t>2026-09-02 00:56:54</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:24</t>
+          <t>2026-09-02 00:56:54</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:25</t>
+          <t>2026-09-02 00:56:55</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:25</t>
+          <t>2026-09-02 00:56:55</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:25</t>
+          <t>2026-09-02 00:56:55</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:25</t>
+          <t>2026-09-02 00:56:55</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-02 00:36:25</t>
+          <t>2026-09-02 00:56:55</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-02_00993A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-02_00993A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:51</t>
+          <t>2026-09-02 01:22:36</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:51</t>
+          <t>2026-09-02 01:22:36</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:51</t>
+          <t>2026-09-02 01:22:36</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:51</t>
+          <t>2026-09-02 01:22:36</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:51</t>
+          <t>2026-09-02 01:22:36</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:51</t>
+          <t>2026-09-02 01:22:36</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:51</t>
+          <t>2026-09-02 01:22:36</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:51</t>
+          <t>2026-09-02 01:22:36</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:51</t>
+          <t>2026-09-02 01:22:36</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:51</t>
+          <t>2026-09-02 01:22:36</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:51</t>
+          <t>2026-09-02 01:22:36</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:51</t>
+          <t>2026-09-02 01:22:36</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:51</t>
+          <t>2026-09-02 01:22:36</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:51</t>
+          <t>2026-09-02 01:22:36</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:51</t>
+          <t>2026-09-02 01:22:36</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:52</t>
+          <t>2026-09-02 01:22:37</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:52</t>
+          <t>2026-09-02 01:22:37</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:52</t>
+          <t>2026-09-02 01:22:37</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:52</t>
+          <t>2026-09-02 01:22:37</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:52</t>
+          <t>2026-09-02 01:22:37</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:52</t>
+          <t>2026-09-02 01:22:37</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:52</t>
+          <t>2026-09-02 01:22:37</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:52</t>
+          <t>2026-09-02 01:22:37</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:52</t>
+          <t>2026-09-02 01:22:37</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:52</t>
+          <t>2026-09-02 01:22:37</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:52</t>
+          <t>2026-09-02 01:22:37</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:52</t>
+          <t>2026-09-02 01:22:37</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:52</t>
+          <t>2026-09-02 01:22:37</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:52</t>
+          <t>2026-09-02 01:22:37</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:52</t>
+          <t>2026-09-02 01:22:37</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:54</t>
+          <t>2026-09-02 01:22:38</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:54</t>
+          <t>2026-09-02 01:22:38</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:54</t>
+          <t>2026-09-02 01:22:38</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:54</t>
+          <t>2026-09-02 01:22:38</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:54</t>
+          <t>2026-09-02 01:22:38</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:54</t>
+          <t>2026-09-02 01:22:38</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:54</t>
+          <t>2026-09-02 01:22:38</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:54</t>
+          <t>2026-09-02 01:22:38</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:54</t>
+          <t>2026-09-02 01:22:38</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:54</t>
+          <t>2026-09-02 01:22:38</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:54</t>
+          <t>2026-09-02 01:22:38</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:54</t>
+          <t>2026-09-02 01:22:38</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:54</t>
+          <t>2026-09-02 01:22:38</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:54</t>
+          <t>2026-09-02 01:22:38</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:54</t>
+          <t>2026-09-02 01:22:38</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:55</t>
+          <t>2026-09-02 01:22:40</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:55</t>
+          <t>2026-09-02 01:22:40</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:55</t>
+          <t>2026-09-02 01:22:40</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:55</t>
+          <t>2026-09-02 01:22:40</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-02 00:56:55</t>
+          <t>2026-09-02 01:22:40</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-02_00993A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-02_00993A_full_holdings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:M66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:36</t>
+          <t>2026-09-02 16:26:36</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,33 +509,33 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+1.46%2440</t>
+          <t>-2.25%2385</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+1.46%</t>
+          <t>-2.25%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2440</v>
+        <v>2385</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.84%378,000</t>
+          <t>8.39%363,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.84%</t>
+          <t>8.39%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>378000</v>
+        <v>363000</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:36</t>
+          <t>2026-09-02 16:26:36</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -565,38 +565,38 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2383台光電子</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+2.83%5640</t>
+          <t>-2.22%5290</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+2.83%</t>
+          <t>-2.22%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5640</v>
+        <v>5290</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.07%114,000</t>
+          <t>5.92%115,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.07%</t>
+          <t>5.92%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>114000</v>
+        <v>115000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:36</t>
+          <t>2026-09-02 16:26:36</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,38 +626,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>2383台光電子</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+5.46%5410</t>
+          <t>-3.46%5445</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+5.46%</t>
+          <t>-3.46%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>5410</v>
+        <v>5445</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5.73%115,000</t>
+          <t>5.68%106,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.73%</t>
+          <t>5.68%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>115000</v>
+        <v>106000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.30%</t>
+          <t>-0.20%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:36</t>
+          <t>2026-09-02 16:26:36</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -687,38 +687,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-2.8%971</t>
+          <t>-2.93%3310</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.93%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>971</v>
+        <v>3310</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.46%563,000</t>
+          <t>4.34%134,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.46%</t>
+          <t>4.34%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>563000</v>
+        <v>134000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:36</t>
+          <t>2026-09-02 16:26:36</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -748,38 +748,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.44%3410</t>
+          <t>+0.21%973</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-0.44%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3410</v>
+        <v>973</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.26%158,000</t>
+          <t>4.19%454,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.26%</t>
+          <t>4.19%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>158000</v>
+        <v>454000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:36</t>
+          <t>2026-09-02 16:26:36</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -809,38 +809,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2059川湖</t>
+          <t>2454聯發科</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-0.21%14150</t>
+          <t>-0.93%4275</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>-0.93%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>14150</v>
+        <v>4275</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.41%32,000</t>
+          <t>4.18%102,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.41%</t>
+          <t>4.18%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>32000</v>
+        <v>102000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:36</t>
+          <t>2026-09-02 16:26:36</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>2059川湖</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+1.05%1450</t>
+          <t>-2.01%13865</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+1.05%</t>
+          <t>-2.01%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1450</v>
+        <v>13865</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.26%306,000</t>
+          <t>4.04%30,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.26%</t>
+          <t>4.04%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>306000</v>
+        <v>30000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:36</t>
+          <t>2026-09-02 16:26:36</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,12 +936,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-4.6%518</t>
+          <t>0%518</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-4.6%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -949,20 +949,20 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.10%778,000</t>
+          <t>3.76%763,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.10%</t>
+          <t>3.76%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>778000</v>
+        <v>763000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.20%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:36</t>
+          <t>2026-09-02 16:26:36</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,38 +992,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>5274信驊科技</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+6.57%17120</t>
+          <t>0%2610</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+6.57%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>17120</v>
+        <v>2610</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.99%25,600</t>
+          <t>3.49%47,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.99%</t>
+          <t>3.49%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>25600</v>
+        <v>47000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:36</t>
+          <t>2026-09-02 16:26:36</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+9.94%4315</t>
+          <t>-2.76%1410</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+9.94%</t>
+          <t>-2.76%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>4315</v>
+        <v>1410</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.89%102,000</t>
+          <t>3.43%249,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.89%</t>
+          <t>3.43%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>102000</v>
+        <v>249000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:36</t>
+          <t>2026-09-02 16:26:36</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>5274信驊科技</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+9.94%7800</t>
+          <t>+3.53%17725</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+9.94%</t>
+          <t>+3.53%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>7800</v>
+        <v>17725</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.79%55,000</t>
+          <t>3.35%20,600</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.79%</t>
+          <t>3.35%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>55000</v>
+        <v>20600</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.35%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:36</t>
+          <t>2026-09-02 16:26:36</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,33 +1180,33 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+8.35%2205</t>
+          <t>-2.95%2140</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+8.35%</t>
+          <t>-2.95%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2205</v>
+        <v>2140</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.98%151,000</t>
+          <t>2.94%140,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.98%</t>
+          <t>2.94%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>151000</v>
+        <v>140000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.23%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:36</t>
+          <t>2026-09-02 16:26:36</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>3443創意電子</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-0.41%1225</t>
+          <t>-1.67%5895</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>-1.67%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1225</v>
+        <v>5895</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.95%247,000</t>
+          <t>2.85%50,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.95%</t>
+          <t>2.85%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>247000</v>
+        <v>50000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:36</t>
+          <t>2026-09-02 16:26:36</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2344華邦電子</t>
+          <t>3189景碩科技</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-3.56%176</t>
+          <t>-3.09%847</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-3.56%</t>
+          <t>-3.09%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>176</v>
+        <v>847</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.85%1,610,000</t>
+          <t>2.53%304,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.85%</t>
+          <t>2.53%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>1610000</v>
+        <v>304000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:36</t>
+          <t>2026-09-02 16:26:36</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,34 +1358,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3443創意電子</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-1.72%5995</t>
+          <t>-2.04%1200</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-1.72%</t>
+          <t>-2.04%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5995</v>
+        <v>1200</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.84%48,000</t>
+          <t>2.52%216,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.84%</t>
+          <t>2.52%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>48000</v>
+        <v>216000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:37</t>
+          <t>2026-09-02 16:26:37</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3189景碩科技</t>
+          <t>2344華邦電子</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+6.72%874</t>
+          <t>+1.7%179</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+6.72%</t>
+          <t>+1.7%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>874</v>
+        <v>179</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.82%354,000</t>
+          <t>2.50%1,496,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.82%</t>
+          <t>2.50%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>354000</v>
+        <v>1496000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:37</t>
+          <t>2026-09-02 16:26:37</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,33 +1485,33 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+9.94%6910</t>
+          <t>+2.03%7050</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+9.94%</t>
+          <t>+2.03%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>6910</v>
+        <v>7050</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.38%39,000</t>
+          <t>2.23%34,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.38%</t>
+          <t>2.23%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>39000</v>
+        <v>34000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:37</t>
+          <t>2026-09-02 16:26:37</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-1.75%5885</t>
+          <t>-6.26%2170</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-1.75%</t>
+          <t>-6.26%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5885</v>
+        <v>2170</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.09%36,000</t>
+          <t>1.98%90,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.09%</t>
+          <t>1.98%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>36000</v>
+        <v>90000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:37</t>
+          <t>2026-09-02 16:26:37</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,25 +1607,25 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+1.36%1865</t>
+          <t>-7.24%1730</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+1.36%</t>
+          <t>-7.24%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1865</v>
+        <v>1730</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.97%110,000</t>
+          <t>1.95%110,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>1.95%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:37</t>
+          <t>2026-09-02 16:26:37</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>1303南亞</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+6.68%2315</t>
+          <t>+1.28%237.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+6.68%</t>
+          <t>+1.28%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>2315</v>
+        <v>237.5</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.85%88,000</t>
+          <t>1.83%821,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.85%</t>
+          <t>1.83%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>88000</v>
+        <v>821000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:37</t>
+          <t>2026-09-02 16:26:37</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,33 +1729,33 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+2.71%132.5</t>
+          <t>-4.91%126</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+2.71%</t>
+          <t>-4.91%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>132.5</v>
+        <v>126</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.80%1,435,000</t>
+          <t>1.69%1,338,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>1.69%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>1435000</v>
+        <v>1338000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:37</t>
+          <t>2026-09-02 16:26:37</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>7769鴻勁</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+0.17%5870</t>
+          <t>-1.95%5770</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>-1.95%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>5870</v>
+        <v>5770</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.48%26,000</t>
+          <t>1.62%29,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.62%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>26000</v>
+        <v>29000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:37</t>
+          <t>2026-09-02 16:26:37</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>5289宜鼎國際</t>
+          <t>2368金像電子</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0%1450</t>
+          <t>-4.08%1175</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-4.08%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1450</v>
+        <v>1175</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.34%94,872</t>
+          <t>1.32%113,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>1.32%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>94872</v>
+        <v>113000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:37</t>
+          <t>2026-09-02 16:26:37</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2327國巨*</t>
+          <t>3081聯亞光電</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+4.22%568</t>
+          <t>-0.88%3395</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+4.22%</t>
+          <t>-0.88%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>568</v>
+        <v>3395</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.29%243,000</t>
+          <t>1.20%37,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.20%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>243000</v>
+        <v>37000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:37</t>
+          <t>2026-09-02 16:26:37</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>2327國巨*</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+4.45%610</t>
+          <t>-4.93%540</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+4.45%</t>
+          <t>-4.93%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>610</v>
+        <v>540</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.13%200,000</t>
+          <t>1.09%202,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>1.09%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>200000</v>
+        <v>202000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:37</t>
+          <t>2026-09-02 16:26:37</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3081聯亞光電</t>
+          <t>3231緯創</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-2.97%3425</t>
+          <t>+1.92%185.5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-2.97%</t>
+          <t>+1.92%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>3425</v>
+        <v>185.5</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.86%25,000</t>
+          <t>1.06%611,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>1.06%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>25000</v>
+        <v>611000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:37</t>
+          <t>2026-09-02 16:26:37</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>8299群聯電子</t>
+          <t>5289宜鼎國際</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-1.85%2125</t>
+          <t>-2.07%1420</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-1.85%</t>
+          <t>-2.07%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>2125</v>
+        <v>1420</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.76%36,000</t>
+          <t>1.02%73,872</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>1.02%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>36000</v>
+        <v>73872</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:37</t>
+          <t>2026-09-02 16:26:37</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,38 +2151,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2337旺宏</t>
+          <t>3008大立光電</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-2.78%122.5</t>
+          <t>+3.03%7810</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-2.78%</t>
+          <t>+3.03%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>122.5</v>
+        <v>7810</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.54%444,000</t>
+          <t>0.94%13,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.94%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>444000</v>
+        <v>13000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:37</t>
+          <t>2026-09-02 16:26:37</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,38 +2212,38 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2301光寶科技</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-1.48%300.5</t>
+          <t>+7.66%1265</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-1.48%</t>
+          <t>+7.66%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>300.5</v>
+        <v>1265</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.52%175,000</t>
+          <t>0.92%82,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.92%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>175000</v>
+        <v>82000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:37</t>
+          <t>2026-09-02 16:26:37</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2455全新</t>
+          <t>4958臻鼎-KY</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+9.85%524</t>
+          <t>-5.23%507</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+9.85%</t>
+          <t>-5.23%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>524</v>
+        <v>507</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.52%113,000</t>
+          <t>0.87%171,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.87%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>113000</v>
+        <v>171000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:38</t>
+          <t>2026-09-02 16:26:38</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>6187萬潤科技</t>
+          <t>3264欣銓</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+2.23%1375</t>
+          <t>-1.68%233.5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+2.23%</t>
+          <t>-1.68%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1375</v>
+        <v>233.5</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.50%38,000</t>
+          <t>0.83%367,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.83%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>38000</v>
+        <v>367000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:38</t>
+          <t>2026-09-02 16:26:38</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2467志聖</t>
+          <t>6805富世達</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+1.79%624</t>
+          <t>-7.66%2110</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+1.79%</t>
+          <t>-7.66%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>624</v>
+        <v>2110</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.49%82,000</t>
+          <t>0.78%36,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.78%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>82000</v>
+        <v>36000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:38</t>
+          <t>2026-09-02 16:26:38</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,38 +2456,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2885元大金</t>
+          <t>6139亞翔工程</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+1.99%66.7</t>
+          <t>0%721</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+1.99%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>66.7</v>
+        <v>721</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.49%773,360</t>
+          <t>0.75%102,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>773360</v>
+        <v>102000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:38</t>
+          <t>2026-09-02 16:26:38</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,38 +2517,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2347聯強</t>
+          <t>7769鴻勁</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-1.15%86</t>
+          <t>-2.73%5710</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-1.15%</t>
+          <t>-2.73%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>86</v>
+        <v>5710</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.48%567,000</t>
+          <t>0.73%13,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.73%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>567000</v>
+        <v>13000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:38</t>
+          <t>2026-09-02 16:26:38</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,38 +2578,38 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2883凱基金控</t>
+          <t>2337旺宏</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+3.25%34.95</t>
+          <t>+0.41%123</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+3.25%</t>
+          <t>+0.41%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>34.95</v>
+        <v>123</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.48%1,458,000</t>
+          <t>0.64%550,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.64%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>1458000</v>
+        <v>550000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:38</t>
+          <t>2026-09-02 16:26:38</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,38 +2639,38 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2368金像電子</t>
+          <t>8299群聯電子</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+5.15%1225</t>
+          <t>-2.82%2065</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+5.15%</t>
+          <t>-2.82%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1225</v>
+        <v>2065</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.46%41,000</t>
+          <t>0.63%31,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.63%</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>41000</v>
+        <v>31000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:38</t>
+          <t>2026-09-02 16:26:38</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,38 +2700,38 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>8358金居開發</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-2.59%526</t>
+          <t>-3.44%589</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-2.59%</t>
+          <t>-3.44%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>526</v>
+        <v>589</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.46%87,000</t>
+          <t>0.58%100,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.58%</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>87000</v>
+        <v>100000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:38</t>
+          <t>2026-09-02 16:26:38</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,38 +2761,38 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2890永豐金控</t>
+          <t>2455全新</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+0.97%41.5</t>
+          <t>+3.44%542</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+0.97%</t>
+          <t>+3.44%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>41.5</v>
+        <v>542</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.45%1,134,220</t>
+          <t>0.56%113,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.56%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>1134220</v>
+        <v>113000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:38</t>
+          <t>2026-09-02 16:26:38</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,38 +2822,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>3231緯創</t>
+          <t>8358金居開發</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+2.25%182</t>
+          <t>-4.37%503</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+2.25%</t>
+          <t>-4.37%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>182</v>
+        <v>503</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.45%260,000</t>
+          <t>0.54%108,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>260000</v>
+        <v>108000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:38</t>
+          <t>2026-09-02 16:26:38</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,25 +2883,25 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>3264欣銓</t>
+          <t>2347聯強</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+4.17%237.5</t>
+          <t>+1.63%87.4</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+4.17%</t>
+          <t>+1.63%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>237.5</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.43%195,000</t>
+          <t>0.43%524,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2910,11 +2910,11 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>195000</v>
+        <v>524000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:38</t>
+          <t>2026-09-02 16:26:38</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,38 +2944,38 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>3491昇達科技</t>
+          <t>6147頎邦</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+7.25%1480</t>
+          <t>-0.54%182.5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+7.25%</t>
+          <t>-0.54%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1480</v>
+        <v>182.5</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.43%32,000</t>
+          <t>0.30%173,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>32000</v>
+        <v>173000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:38</t>
+          <t>2026-09-02 16:26:38</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,38 +3005,38 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>8210勤誠興業</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+3.57%2030</t>
+          <t>-2.22%968</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+3.57%</t>
+          <t>-2.22%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>2030</v>
+        <v>968</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.42%22,000</t>
+          <t>0.30%32,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>22000</v>
+        <v>32000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:38</t>
+          <t>2026-09-02 16:26:38</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,38 +3066,38 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>6584南俊國際</t>
+          <t>2885元大金</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+6.04%667</t>
+          <t>0%66.7</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+6.04%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>667</v>
+        <v>66.7</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.40%65,000</t>
+          <t>0.28%439,360</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>65000</v>
+        <v>439360</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:38</t>
+          <t>2026-09-02 16:26:38</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,38 +3127,38 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2395研華</t>
+          <t>3036文曄</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+5.02%711</t>
+          <t>-4.59%187</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+5.02%</t>
+          <t>-4.59%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>711</v>
+        <v>187</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.39%59,000</t>
+          <t>0.28%149,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>59000</v>
+        <v>149000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:38</t>
+          <t>2026-09-02 16:26:38</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,38 +3188,38 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>2301光寶科技</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0%1175</t>
+          <t>+4.83%315</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+4.83%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>1175</v>
+        <v>315</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.39%34,000</t>
+          <t>0.25%87,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.25%</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>34000</v>
+        <v>87000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:40</t>
+          <t>2026-09-02 16:26:40</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3249,38 +3249,38 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1560中砂</t>
+          <t>6187萬潤科技</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+8.93%744</t>
+          <t>-2.55%1340</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+8.93%</t>
+          <t>-2.55%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>744</v>
+        <v>1340</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.38%57,000</t>
+          <t>0.25%19,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.25%</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>57000</v>
+        <v>19000</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:40</t>
+          <t>2026-09-02 16:26:40</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3310,38 +3310,38 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>6196帆宣</t>
+          <t>2467志聖</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+4.54%507</t>
+          <t>-2.4%609</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+4.54%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>507</v>
+        <v>609</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.37%79,000</t>
+          <t>0.24%41,000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.24%</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>79000</v>
+        <v>41000</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:40</t>
+          <t>2026-09-02 16:26:40</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3371,38 +3371,38 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>6139亞翔工程</t>
+          <t>2883凱基金控</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>+1.99%770</t>
+          <t>+1.57%35.5</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>+1.99%</t>
+          <t>+1.57%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>770</v>
+        <v>35.5</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.35%48,000</t>
+          <t>0.24%729,000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.24%</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>48000</v>
+        <v>729000</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:40</t>
+          <t>2026-09-02 16:26:40</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3432,38 +3432,38 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>6213聯茂</t>
+          <t>3131弘塑科技</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>+0.36%550</t>
+          <t>-3.02%2405</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>-3.02%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>550</v>
+        <v>2405</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.35%66,000</t>
+          <t>0.24%10,000</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.24%</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>66000</v>
+        <v>10000</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-02 01:22:40</t>
+          <t>2026-09-02 16:26:40</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3493,41 +3493,956 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
+          <t>3491昇達科技</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>-2.36%1445</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-2.36%</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>1445</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.23%16,000</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.23%</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>16000</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-09-02 16:26:40</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>4</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2890永豐金控</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>+1.57%42.15</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>+1.57%</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>42.15</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.22%566,220</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.22%</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>566220</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-09-02 16:26:40</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>4</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2360致茂</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>-2.71%1975</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-2.71%</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>1975</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>0.21%11,000</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>0.21%</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>11000</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-09-02 16:26:40</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>4</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>3044健鼎科技</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>-0.2%502</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>502</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>0.21%43,000</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>0.21%</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>43000</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-09-02 16:26:40</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>4</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>6239力成</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>-2.11%278</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-2.11%</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>278</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>0.21%77,000</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>0.21%</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>77000</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-09-02 16:26:40</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>4</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>1560中砂</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>-5.38%704</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-5.38%</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>704</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>0.20%28,000</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>0.20%</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>28000</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-09-02 16:26:40</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>4</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2395研華</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>-2.67%692</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-2.67%</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>692</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>0.20%29,000</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>0.20%</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>29000</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-09-02 16:26:40</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>4</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>6584南俊國際</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>-1.35%658</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-1.35%</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>658</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>0.20%32,000</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>0.20%</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
+        <v>32000</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-09-02 16:26:40</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>4</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2313華通</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>-1.19%249</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-1.19%</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>249</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>0.19%78,000</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>0.19%</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
+        <v>78000</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-09-02 16:26:40</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>4</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>6196帆宣</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>-2.96%492</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-2.96%</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>492</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>0.19%39,000</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>0.19%</t>
+        </is>
+      </c>
+      <c r="K60" t="n">
+        <v>39000</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-09-02 16:26:40</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>4</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>6415矽力*-KY</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>+1.79%426</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>+1.79%</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>426</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>0.18%45,000</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>0.18%</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
+        <v>45000</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-09-02 16:26:41</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>5</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>3042晶技</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>-1.1%180</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-1.1%</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>180</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>0.17%97,000</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>0.17%</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
+        <v>97000</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-09-02 16:26:41</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>5</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>3702大聯大</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>+1.49%102</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>+1.49%</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>102</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>0.17%177,000</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>0.17%</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
+        <v>177000</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-09-02 16:26:41</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>5</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>6213聯茂</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>-2.55%536</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-2.55%</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>536</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>0.17%33,000</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>0.17%</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
+        <v>33000</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-09-02 16:26:41</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>5</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2449京元電子</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>-3.05%270.5</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-3.05%</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>270.5</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>0.16%59,000</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>0.16%</t>
+        </is>
+      </c>
+      <c r="K65" t="n">
+        <v>59000</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-09-02 16:26:41</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>5</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
           <t>3661世芯-KY</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>+4.91%4275</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>+4.91%</t>
-        </is>
-      </c>
-      <c r="H51" t="n">
-        <v>4275</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>0.32%8,000</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>0.32%</t>
-        </is>
-      </c>
-      <c r="K51" t="n">
-        <v>8000</v>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>+0.02%</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>-1.75%4200</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>-1.75%</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>4200</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>0.16%4,000</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>0.16%</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
+        <v>4000</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
         <is>
           <t>登入查看</t>
         </is>

--- a/etf_holdings/2026-09-02_00993A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-02_00993A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:36</t>
+          <t>2026-09-02 19:49:51</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:36</t>
+          <t>2026-09-02 19:49:51</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:36</t>
+          <t>2026-09-02 19:49:51</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:36</t>
+          <t>2026-09-02 19:49:51</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:36</t>
+          <t>2026-09-02 19:49:51</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:36</t>
+          <t>2026-09-02 19:49:51</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:36</t>
+          <t>2026-09-02 19:49:51</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:36</t>
+          <t>2026-09-02 19:49:51</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:36</t>
+          <t>2026-09-02 19:49:51</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:36</t>
+          <t>2026-09-02 19:49:51</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:36</t>
+          <t>2026-09-02 19:49:51</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:36</t>
+          <t>2026-09-02 19:49:51</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:36</t>
+          <t>2026-09-02 19:49:51</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:36</t>
+          <t>2026-09-02 19:49:51</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:36</t>
+          <t>2026-09-02 19:49:51</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:37</t>
+          <t>2026-09-02 19:49:53</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:37</t>
+          <t>2026-09-02 19:49:53</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:37</t>
+          <t>2026-09-02 19:49:53</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:37</t>
+          <t>2026-09-02 19:49:53</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:37</t>
+          <t>2026-09-02 19:49:53</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:37</t>
+          <t>2026-09-02 19:49:53</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:37</t>
+          <t>2026-09-02 19:49:53</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:37</t>
+          <t>2026-09-02 19:49:53</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:37</t>
+          <t>2026-09-02 19:49:53</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:37</t>
+          <t>2026-09-02 19:49:53</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:37</t>
+          <t>2026-09-02 19:49:53</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:37</t>
+          <t>2026-09-02 19:49:53</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:37</t>
+          <t>2026-09-02 19:49:53</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:37</t>
+          <t>2026-09-02 19:49:53</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:37</t>
+          <t>2026-09-02 19:49:53</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:38</t>
+          <t>2026-09-02 19:49:54</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:38</t>
+          <t>2026-09-02 19:49:54</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:38</t>
+          <t>2026-09-02 19:49:54</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:38</t>
+          <t>2026-09-02 19:49:54</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:38</t>
+          <t>2026-09-02 19:49:54</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:38</t>
+          <t>2026-09-02 19:49:54</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:38</t>
+          <t>2026-09-02 19:49:54</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:38</t>
+          <t>2026-09-02 19:49:54</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:38</t>
+          <t>2026-09-02 19:49:54</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:38</t>
+          <t>2026-09-02 19:49:54</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:38</t>
+          <t>2026-09-02 19:49:54</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:38</t>
+          <t>2026-09-02 19:49:54</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:38</t>
+          <t>2026-09-02 19:49:54</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:38</t>
+          <t>2026-09-02 19:49:54</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:38</t>
+          <t>2026-09-02 19:49:54</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:40</t>
+          <t>2026-09-02 19:49:55</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:40</t>
+          <t>2026-09-02 19:49:55</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:40</t>
+          <t>2026-09-02 19:49:55</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:40</t>
+          <t>2026-09-02 19:49:55</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:40</t>
+          <t>2026-09-02 19:49:55</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:40</t>
+          <t>2026-09-02 19:49:55</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:40</t>
+          <t>2026-09-02 19:49:55</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:40</t>
+          <t>2026-09-02 19:49:55</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:40</t>
+          <t>2026-09-02 19:49:55</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:40</t>
+          <t>2026-09-02 19:49:55</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:40</t>
+          <t>2026-09-02 19:49:55</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:40</t>
+          <t>2026-09-02 19:49:55</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:40</t>
+          <t>2026-09-02 19:49:55</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:40</t>
+          <t>2026-09-02 19:49:55</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:40</t>
+          <t>2026-09-02 19:49:55</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:41</t>
+          <t>2026-09-02 19:49:57</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:41</t>
+          <t>2026-09-02 19:49:57</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:41</t>
+          <t>2026-09-02 19:49:57</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:41</t>
+          <t>2026-09-02 19:49:57</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-09-02 16:26:41</t>
+          <t>2026-09-02 19:49:57</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
